--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/92.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/92.xlsx
@@ -426,13 +426,13 @@
         <v>-9.964649976408918</v>
       </c>
       <c r="E2">
-        <v>-15.86337785132309</v>
+        <v>-7.755525532405956</v>
       </c>
       <c r="F2">
-        <v>-3.556192176242022</v>
+        <v>-2.72886437453303</v>
       </c>
       <c r="G2">
-        <v>-9.876226414506993</v>
+        <v>-6.008443845431261</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.570601519736334</v>
       </c>
       <c r="E3">
-        <v>-16.05996796494407</v>
+        <v>-10.07170413310911</v>
       </c>
       <c r="F3">
-        <v>-3.399943859991173</v>
+        <v>-2.8577782232263</v>
       </c>
       <c r="G3">
-        <v>-9.490292415906664</v>
+        <v>-5.40336034009718</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.151532228421731</v>
       </c>
       <c r="E4">
-        <v>-17.32755576680112</v>
+        <v>-8.969002598345352</v>
       </c>
       <c r="F4">
-        <v>-3.326906706086341</v>
+        <v>-2.60051298730626</v>
       </c>
       <c r="G4">
-        <v>-9.876521724447343</v>
+        <v>-5.944765178627118</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.770890448003339</v>
       </c>
       <c r="E5">
-        <v>-17.6772309442514</v>
+        <v>-11.45631676027238</v>
       </c>
       <c r="F5">
-        <v>-3.546903692554431</v>
+        <v>-2.724090493190696</v>
       </c>
       <c r="G5">
-        <v>-9.277209887836324</v>
+        <v>-6.120116939985403</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.410327498968091</v>
       </c>
       <c r="E6">
-        <v>-17.8265392607583</v>
+        <v>-11.74995660035175</v>
       </c>
       <c r="F6">
-        <v>-3.485177895534826</v>
+        <v>-2.398619970426354</v>
       </c>
       <c r="G6">
-        <v>-9.643945459092341</v>
+        <v>-5.132692373658585</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.068874637815094</v>
       </c>
       <c r="E7">
-        <v>-18.86705126197473</v>
+        <v>-11.47813494804134</v>
       </c>
       <c r="F7">
-        <v>-3.123677532585719</v>
+        <v>-2.335331044117666</v>
       </c>
       <c r="G7">
-        <v>-10.00615950703944</v>
+        <v>-5.113333166457862</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.72723708282615</v>
       </c>
       <c r="E8">
-        <v>-19.00802718630751</v>
+        <v>-12.69120445132004</v>
       </c>
       <c r="F8">
-        <v>-3.183980194407314</v>
+        <v>-2.59854809982682</v>
       </c>
       <c r="G8">
-        <v>-9.241037701365006</v>
+        <v>-5.822959671897411</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.375483045510744</v>
       </c>
       <c r="E9">
-        <v>-19.55596348428761</v>
+        <v>-13.09749461081422</v>
       </c>
       <c r="F9">
-        <v>-3.216478704353944</v>
+        <v>-2.557968037498477</v>
       </c>
       <c r="G9">
-        <v>-8.932655374322154</v>
+        <v>-6.509965435906148</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.00567991034617</v>
       </c>
       <c r="E10">
-        <v>-20.27119066905907</v>
+        <v>-14.51014302055897</v>
       </c>
       <c r="F10">
-        <v>-3.498175808452153</v>
+        <v>-2.022262838108037</v>
       </c>
       <c r="G10">
-        <v>-9.159597782259588</v>
+        <v>-4.328271377366678</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.608877587708115</v>
       </c>
       <c r="E11">
-        <v>-21.44791916842622</v>
+        <v>-13.51949857511501</v>
       </c>
       <c r="F11">
-        <v>-2.972810290983456</v>
+        <v>-2.423053495339328</v>
       </c>
       <c r="G11">
-        <v>-8.494438391393635</v>
+        <v>-4.383343400020398</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.183692449886981</v>
       </c>
       <c r="E12">
-        <v>-21.83074730408665</v>
+        <v>-15.05088810181489</v>
       </c>
       <c r="F12">
-        <v>-2.92012695253281</v>
+        <v>-2.294843758938437</v>
       </c>
       <c r="G12">
-        <v>-7.803875783214458</v>
+        <v>-4.549284617946196</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.720370112717429</v>
       </c>
       <c r="E13">
-        <v>-22.2326493722674</v>
+        <v>-16.30492670944098</v>
       </c>
       <c r="F13">
-        <v>-3.257376859764962</v>
+        <v>-2.109700330943136</v>
       </c>
       <c r="G13">
-        <v>-7.401965516841194</v>
+        <v>-3.483133702743622</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.224396324320416</v>
       </c>
       <c r="E14">
-        <v>-22.98343866342109</v>
+        <v>-17.37913508574849</v>
       </c>
       <c r="F14">
-        <v>-2.963019816649769</v>
+        <v>-1.694571462336789</v>
       </c>
       <c r="G14">
-        <v>-6.084286000556267</v>
+        <v>-3.166318636292996</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.70118943569693</v>
       </c>
       <c r="E15">
-        <v>-23.69860697803045</v>
+        <v>-18.32748811243481</v>
       </c>
       <c r="F15">
-        <v>-2.961623189208649</v>
+        <v>-1.882035147427331</v>
       </c>
       <c r="G15">
-        <v>-5.579233815683417</v>
+        <v>-2.432755619577298</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.165760488155837</v>
       </c>
       <c r="E16">
-        <v>-24.66231153160278</v>
+        <v>-17.84167342089194</v>
       </c>
       <c r="F16">
-        <v>-2.782154906289927</v>
+        <v>-1.635942102668849</v>
       </c>
       <c r="G16">
-        <v>-5.594763837324269</v>
+        <v>-2.520630014160787</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.640627897113189</v>
       </c>
       <c r="E17">
-        <v>-25.30370647615317</v>
+        <v>-18.97208921658264</v>
       </c>
       <c r="F17">
-        <v>-2.557036124170328</v>
+        <v>-1.692785502216353</v>
       </c>
       <c r="G17">
-        <v>-4.908125570130189</v>
+        <v>-1.624128097246183</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.144141929246846</v>
       </c>
       <c r="E18">
-        <v>-25.97153412348634</v>
+        <v>-19.91624887633786</v>
       </c>
       <c r="F18">
-        <v>-2.461595773856783</v>
+        <v>-1.373635422735371</v>
       </c>
       <c r="G18">
-        <v>-3.919565701143804</v>
+        <v>-0.7107114831926414</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.699041018360358</v>
       </c>
       <c r="E19">
-        <v>-27.79701180919235</v>
+        <v>-22.2617538747147</v>
       </c>
       <c r="F19">
-        <v>-2.211999563351861</v>
+        <v>-1.059796835041139</v>
       </c>
       <c r="G19">
-        <v>-3.527807534275462</v>
+        <v>-0.8192116364987998</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.31361152581542</v>
       </c>
       <c r="E20">
-        <v>-27.2012819965353</v>
+        <v>-22.29888736157759</v>
       </c>
       <c r="F20">
-        <v>-2.069569243747111</v>
+        <v>-0.9452617877256628</v>
       </c>
       <c r="G20">
-        <v>-2.71236491476538</v>
+        <v>0.2190620203347321</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.996576747031424</v>
       </c>
       <c r="E21">
-        <v>-28.71979254315736</v>
+        <v>-22.86733764681244</v>
       </c>
       <c r="F21">
-        <v>-2.010359198529808</v>
+        <v>-0.8615105298330216</v>
       </c>
       <c r="G21">
-        <v>-2.768929893228647</v>
+        <v>0.6759950910383249</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.746014886721658</v>
       </c>
       <c r="E22">
-        <v>-28.29169778131625</v>
+        <v>-24.34311751269812</v>
       </c>
       <c r="F22">
-        <v>-2.082698867081484</v>
+        <v>-0.3960285202801038</v>
       </c>
       <c r="G22">
-        <v>-2.763574939643633</v>
+        <v>1.408636084495819</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.556505911859476</v>
       </c>
       <c r="E23">
-        <v>-28.55520062687458</v>
+        <v>-24.10815763881014</v>
       </c>
       <c r="F23">
-        <v>-1.818694033972267</v>
+        <v>-0.4871489345880494</v>
       </c>
       <c r="G23">
-        <v>-2.451688267975294</v>
+        <v>1.288756654821507</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.42212115325544</v>
       </c>
       <c r="E24">
-        <v>-29.51456463811055</v>
+        <v>-24.93020246847453</v>
       </c>
       <c r="F24">
-        <v>-1.598764973631207</v>
+        <v>-0.2614999973306585</v>
       </c>
       <c r="G24">
-        <v>-2.473954637477686</v>
+        <v>0.9236059135787015</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.331866157143459</v>
       </c>
       <c r="E25">
-        <v>-30.2821545678327</v>
+        <v>-24.80541583871917</v>
       </c>
       <c r="F25">
-        <v>-1.541371538128243</v>
+        <v>-0.2206739098836848</v>
       </c>
       <c r="G25">
-        <v>-2.850776683807436</v>
+        <v>0.3467901319792366</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.278468498147357</v>
       </c>
       <c r="E26">
-        <v>-30.19084921065305</v>
+        <v>-24.77603057088339</v>
       </c>
       <c r="F26">
-        <v>-1.391874416210211</v>
+        <v>-0.09639146333946662</v>
       </c>
       <c r="G26">
-        <v>-3.012964184269229</v>
+        <v>1.319242484330307</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.250005529157647</v>
       </c>
       <c r="E27">
-        <v>-30.65221467102851</v>
+        <v>-25.71196652184069</v>
       </c>
       <c r="F27">
-        <v>-1.288731077418033</v>
+        <v>-0.1973313448401976</v>
       </c>
       <c r="G27">
-        <v>-3.748249842303636</v>
+        <v>0.771662386825495</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.238013692779367</v>
       </c>
       <c r="E28">
-        <v>-30.54553514459282</v>
+        <v>-25.65303296110487</v>
       </c>
       <c r="F28">
-        <v>-1.511293517732593</v>
+        <v>-0.1703199405697113</v>
       </c>
       <c r="G28">
-        <v>-3.698204651078985</v>
+        <v>-0.3930859550168335</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.233320570753782</v>
       </c>
       <c r="E29">
-        <v>-29.58173775730333</v>
+        <v>-24.50670863622521</v>
       </c>
       <c r="F29">
-        <v>-1.516229759085875</v>
+        <v>-0.201663706356839</v>
       </c>
       <c r="G29">
-        <v>-3.97755801098543</v>
+        <v>-0.556008449107942</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.227830390356903</v>
       </c>
       <c r="E30">
-        <v>-29.51555637391823</v>
+        <v>-25.16456005531949</v>
       </c>
       <c r="F30">
-        <v>-1.094259404099807</v>
+        <v>-0.3500657265683704</v>
       </c>
       <c r="G30">
-        <v>-4.000962964368949</v>
+        <v>-1.234007259936004</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.216545597519014</v>
       </c>
       <c r="E31">
-        <v>-29.69024452300112</v>
+        <v>-24.84523923914262</v>
       </c>
       <c r="F31">
-        <v>-1.376369863532012</v>
+        <v>-0.452676425120548</v>
       </c>
       <c r="G31">
-        <v>-4.672314020317575</v>
+        <v>0.2935490309556866</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.194319152659085</v>
       </c>
       <c r="E32">
-        <v>-29.95881925944803</v>
+        <v>-23.47584228464513</v>
       </c>
       <c r="F32">
-        <v>-1.597180306789651</v>
+        <v>-0.1851038136074741</v>
       </c>
       <c r="G32">
-        <v>-4.866792022145864</v>
+        <v>-1.007557035232486</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.158917989993477</v>
       </c>
       <c r="E33">
-        <v>-28.59382851016</v>
+        <v>-25.39563449850888</v>
       </c>
       <c r="F33">
-        <v>-1.667992465850564</v>
+        <v>0.0159898287287311</v>
       </c>
       <c r="G33">
-        <v>-4.196976577887058</v>
+        <v>-1.200860359742493</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.108828936711974</v>
       </c>
       <c r="E34">
-        <v>-29.34858927301842</v>
+        <v>-22.66767269934024</v>
       </c>
       <c r="F34">
-        <v>-1.524606210262984</v>
+        <v>-0.5381606276198457</v>
       </c>
       <c r="G34">
-        <v>-4.46742470248117</v>
+        <v>-1.518600730672881</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.045404160197197</v>
       </c>
       <c r="E35">
-        <v>-29.27567631302092</v>
+        <v>-24.09265214380788</v>
       </c>
       <c r="F35">
-        <v>-1.653703128152273</v>
+        <v>0.06599671210093166</v>
       </c>
       <c r="G35">
-        <v>-4.991087976039189</v>
+        <v>-1.572918072367929</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.9736173960021363</v>
       </c>
       <c r="E36">
-        <v>-28.44662140559266</v>
+        <v>-22.64561903092289</v>
       </c>
       <c r="F36">
-        <v>-1.575096031831017</v>
+        <v>-0.5428831501832058</v>
       </c>
       <c r="G36">
-        <v>-5.146752408040806</v>
+        <v>-1.207481864849453</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.8999271210774308</v>
       </c>
       <c r="E37">
-        <v>-27.30640146367535</v>
+        <v>-22.85206310398457</v>
       </c>
       <c r="F37">
-        <v>-1.313478553576668</v>
+        <v>-0.1224071699917879</v>
       </c>
       <c r="G37">
-        <v>-5.410959649228854</v>
+        <v>-1.506653802974943</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.8341997578138</v>
       </c>
       <c r="E38">
-        <v>-27.01884789266229</v>
+        <v>-22.10656307047183</v>
       </c>
       <c r="F38">
-        <v>-1.646300008673454</v>
+        <v>-0.2839379851702887</v>
       </c>
       <c r="G38">
-        <v>-5.536778089925762</v>
+        <v>-2.12659796075175</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.7875184284542995</v>
       </c>
       <c r="E39">
-        <v>-26.86461259643505</v>
+        <v>-21.38089775311269</v>
       </c>
       <c r="F39">
-        <v>-1.606890429485267</v>
+        <v>0.03752655283411545</v>
       </c>
       <c r="G39">
-        <v>-5.100073750136145</v>
+        <v>-0.7239807431790358</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.7708366086640527</v>
       </c>
       <c r="E40">
-        <v>-27.06219897433772</v>
+        <v>-21.0940279816748</v>
       </c>
       <c r="F40">
-        <v>-1.4922692319599</v>
+        <v>0.5380277943403824</v>
       </c>
       <c r="G40">
-        <v>-4.662381762657136</v>
+        <v>-1.439083607401298</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.7969430009274514</v>
       </c>
       <c r="E41">
-        <v>-25.84125898323368</v>
+        <v>-21.10626844691753</v>
       </c>
       <c r="F41">
-        <v>-1.374726382604858</v>
+        <v>0.0001994892965669287</v>
       </c>
       <c r="G41">
-        <v>-5.04857825898222</v>
+        <v>-0.7615474488131184</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.873970578087365</v>
       </c>
       <c r="E42">
-        <v>-25.55978262433892</v>
+        <v>-19.70014556821783</v>
       </c>
       <c r="F42">
-        <v>-1.335854413861088</v>
+        <v>-0.1093926897264049</v>
       </c>
       <c r="G42">
-        <v>-4.911265699162578</v>
+        <v>-1.306732254579536</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.009161897911214</v>
       </c>
       <c r="E43">
-        <v>-24.91124174780441</v>
+        <v>-18.77422207329149</v>
       </c>
       <c r="F43">
-        <v>-1.024663288386204</v>
+        <v>0.1432825624147227</v>
       </c>
       <c r="G43">
-        <v>-5.077098636776913</v>
+        <v>-1.074667859787809</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.203046743817381</v>
       </c>
       <c r="E44">
-        <v>-24.69353083141165</v>
+        <v>-19.82716020718497</v>
       </c>
       <c r="F44">
-        <v>-1.18447358446909</v>
+        <v>-0.01540281073516176</v>
       </c>
       <c r="G44">
-        <v>-4.935113617456622</v>
+        <v>-0.9459094445736387</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.451828756724034</v>
       </c>
       <c r="E45">
-        <v>-24.35542137657696</v>
+        <v>-19.46703784019899</v>
       </c>
       <c r="F45">
-        <v>-1.269816964509912</v>
+        <v>0.2411086108483304</v>
       </c>
       <c r="G45">
-        <v>-5.466048077990371</v>
+        <v>-0.4105158039406038</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.747005381303202</v>
       </c>
       <c r="E46">
-        <v>-24.07891728214262</v>
+        <v>-18.7139480842494</v>
       </c>
       <c r="F46">
-        <v>-1.382912309279323</v>
+        <v>-0.306615371189328</v>
       </c>
       <c r="G46">
-        <v>-4.57845467760966</v>
+        <v>-1.301505268635341</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.07304109441087</v>
       </c>
       <c r="E47">
-        <v>-23.24298362269671</v>
+        <v>-18.47439633771765</v>
       </c>
       <c r="F47">
-        <v>-1.197554334126697</v>
+        <v>-0.09475792282114599</v>
       </c>
       <c r="G47">
-        <v>-4.886403883406665</v>
+        <v>-0.6800451864980711</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.417886754548659</v>
       </c>
       <c r="E48">
-        <v>-22.59735908342315</v>
+        <v>-17.70946915071201</v>
       </c>
       <c r="F48">
-        <v>-0.9234682697254106</v>
+        <v>0.3403793320324203</v>
       </c>
       <c r="G48">
-        <v>-4.713604912421628</v>
+        <v>-1.059784238794168</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.764796914071423</v>
       </c>
       <c r="E49">
-        <v>-22.09194968484908</v>
+        <v>-18.6053779199155</v>
       </c>
       <c r="F49">
-        <v>-1.168613662175091</v>
+        <v>-0.06975945133946251</v>
       </c>
       <c r="G49">
-        <v>-5.090020087278007</v>
+        <v>-0.7114431956003976</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.101432410402415</v>
       </c>
       <c r="E50">
-        <v>-22.20132138908233</v>
+        <v>-17.02336005380987</v>
       </c>
       <c r="F50">
-        <v>-1.034500979661851</v>
+        <v>-0.1871589931338196</v>
       </c>
       <c r="G50">
-        <v>-5.160691037225327</v>
+        <v>-1.222837981747654</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.415016251602801</v>
       </c>
       <c r="E51">
-        <v>-21.0891327012725</v>
+        <v>-15.24160025617392</v>
       </c>
       <c r="F51">
-        <v>-1.316440795409079</v>
+        <v>-0.4284027751163141</v>
       </c>
       <c r="G51">
-        <v>-5.252394617368688</v>
+        <v>-0.5657372710316956</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.696631824758217</v>
       </c>
       <c r="E52">
-        <v>-20.96319131064518</v>
+        <v>-16.40519165244481</v>
       </c>
       <c r="F52">
-        <v>-1.113760829496513</v>
+        <v>-0.1433681787522266</v>
       </c>
       <c r="G52">
-        <v>-5.06305828972405</v>
+        <v>-0.7896543926913219</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.943313695804798</v>
       </c>
       <c r="E53">
-        <v>-21.49380166707193</v>
+        <v>-15.60565786707256</v>
       </c>
       <c r="F53">
-        <v>-1.429522886300045</v>
+        <v>-0.03023224398007851</v>
       </c>
       <c r="G53">
-        <v>-5.652152402398957</v>
+        <v>-0.9205718516916066</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.152491643275731</v>
       </c>
       <c r="E54">
-        <v>-20.43571012975773</v>
+        <v>-14.99272438166037</v>
       </c>
       <c r="F54">
-        <v>-1.491812801520957</v>
+        <v>-0.6320602145641837</v>
       </c>
       <c r="G54">
-        <v>-5.902427576845603</v>
+        <v>-1.673733604781868</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.330842106502085</v>
       </c>
       <c r="E55">
-        <v>-20.35532971612158</v>
+        <v>-14.81736375418734</v>
       </c>
       <c r="F55">
-        <v>-1.142491924495211</v>
+        <v>0.1517493056387365</v>
       </c>
       <c r="G55">
-        <v>-6.351557902680836</v>
+        <v>-1.936454452603488</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.481396537212496</v>
       </c>
       <c r="E56">
-        <v>-19.53530911433863</v>
+        <v>-14.74151634303287</v>
       </c>
       <c r="F56">
-        <v>-1.498973209350756</v>
+        <v>-0.2764569991556063</v>
       </c>
       <c r="G56">
-        <v>-6.553487558670623</v>
+        <v>-2.283853785209697</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.612933517580909</v>
       </c>
       <c r="E57">
-        <v>-19.60758808797505</v>
+        <v>-14.08149578488892</v>
       </c>
       <c r="F57">
-        <v>-1.444612426909441</v>
+        <v>-0.2752790607088255</v>
       </c>
       <c r="G57">
-        <v>-5.872588147984012</v>
+        <v>-2.0023282566309</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.731533717427544</v>
       </c>
       <c r="E58">
-        <v>-19.21410445297457</v>
+        <v>-13.73539357343069</v>
       </c>
       <c r="F58">
-        <v>-1.359025506852196</v>
+        <v>-0.2919267604028871</v>
       </c>
       <c r="G58">
-        <v>-6.565637922105247</v>
+        <v>-2.570127241385011</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.843358035404541</v>
       </c>
       <c r="E59">
-        <v>-18.66595531671611</v>
+        <v>-13.40922117608022</v>
       </c>
       <c r="F59">
-        <v>-1.477940132626274</v>
+        <v>-0.6201176417180233</v>
       </c>
       <c r="G59">
-        <v>-7.126782589536804</v>
+        <v>-2.523609363336763</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.953204657138306</v>
       </c>
       <c r="E60">
-        <v>-18.87916492994524</v>
+        <v>-13.6621319209346</v>
       </c>
       <c r="F60">
-        <v>-1.63420253112297</v>
+        <v>-0.6934231866613627</v>
       </c>
       <c r="G60">
-        <v>-6.961251524305936</v>
+        <v>-1.963718122540914</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.060558372670203</v>
       </c>
       <c r="E61">
-        <v>-18.09118328176656</v>
+        <v>-12.29923785511212</v>
       </c>
       <c r="F61">
-        <v>-1.582844580516803</v>
+        <v>-0.2728130109506913</v>
       </c>
       <c r="G61">
-        <v>-7.429068406922207</v>
+        <v>-2.770938000823027</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.16609624236621</v>
       </c>
       <c r="E62">
-        <v>-17.27925959150932</v>
+        <v>-13.1380470955529</v>
       </c>
       <c r="F62">
-        <v>-1.717263758969079</v>
+        <v>-0.6336862997758792</v>
       </c>
       <c r="G62">
-        <v>-7.267514182221388</v>
+        <v>-3.035936016406902</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.26408169543924</v>
       </c>
       <c r="E63">
-        <v>-17.24041434147152</v>
+        <v>-12.21430632509827</v>
       </c>
       <c r="F63">
-        <v>-1.489584493207426</v>
+        <v>-0.6081841809132936</v>
       </c>
       <c r="G63">
-        <v>-7.602546590770049</v>
+        <v>-3.649737727424427</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.352068014743169</v>
       </c>
       <c r="E64">
-        <v>-17.5374822363747</v>
+        <v>-11.99627841552497</v>
       </c>
       <c r="F64">
-        <v>-1.974820580214904</v>
+        <v>-0.5244950505758623</v>
       </c>
       <c r="G64">
-        <v>-7.999699085882119</v>
+        <v>-3.83254770538733</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.423403016135717</v>
       </c>
       <c r="E65">
-        <v>-17.73395913814549</v>
+        <v>-11.42017500921716</v>
       </c>
       <c r="F65">
-        <v>-1.869221960440829</v>
+        <v>-0.5365345424081504</v>
       </c>
       <c r="G65">
-        <v>-8.012289133005709</v>
+        <v>-4.625618956305118</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.474017134283319</v>
       </c>
       <c r="E66">
-        <v>-17.08633754183454</v>
+        <v>-11.38558199627257</v>
       </c>
       <c r="F66">
-        <v>-1.808032945498238</v>
+        <v>-0.7076851882353618</v>
       </c>
       <c r="G66">
-        <v>-8.637486526499186</v>
+        <v>-3.504848827024027</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.499545219634805</v>
       </c>
       <c r="E67">
-        <v>-17.45230164029041</v>
+        <v>-11.26960777693613</v>
       </c>
       <c r="F67">
-        <v>-1.953403141015523</v>
+        <v>-0.6117188246210391</v>
       </c>
       <c r="G67">
-        <v>-8.491990600110288</v>
+        <v>-4.455192308507559</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.498172423362294</v>
       </c>
       <c r="E68">
-        <v>-17.68097146378174</v>
+        <v>-11.18479398724647</v>
       </c>
       <c r="F68">
-        <v>-2.254997630128975</v>
+        <v>-1.230313779805209</v>
       </c>
       <c r="G68">
-        <v>-8.576498461373786</v>
+        <v>-4.679073336730032</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.472263372848039</v>
       </c>
       <c r="E69">
-        <v>-16.78877151479053</v>
+        <v>-10.57513911701584</v>
       </c>
       <c r="F69">
-        <v>-2.055097665220204</v>
+        <v>-1.316412630917384</v>
       </c>
       <c r="G69">
-        <v>-8.782480425989489</v>
+        <v>-4.573883935977353</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.422519742736768</v>
       </c>
       <c r="E70">
-        <v>-17.13892218201161</v>
+        <v>-10.63716562549889</v>
       </c>
       <c r="F70">
-        <v>-2.107879579391783</v>
+        <v>-1.316570849091319</v>
       </c>
       <c r="G70">
-        <v>-8.726148414256942</v>
+        <v>-4.148047001992618</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.3553942129564</v>
       </c>
       <c r="E71">
-        <v>-16.7484318683302</v>
+        <v>-10.93772497386199</v>
       </c>
       <c r="F71">
-        <v>-2.267918504877842</v>
+        <v>-0.9056931619961388</v>
       </c>
       <c r="G71">
-        <v>-8.491340918241518</v>
+        <v>-4.933263008497095</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.274759162029769</v>
       </c>
       <c r="E72">
-        <v>-17.31653798954046</v>
+        <v>-11.42704923276081</v>
       </c>
       <c r="F72">
-        <v>-2.317831782733526</v>
+        <v>-1.116155639658006</v>
       </c>
       <c r="G72">
-        <v>-8.264382104196287</v>
+        <v>-4.953787049351422</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.186933769004807</v>
       </c>
       <c r="E73">
-        <v>-16.91164260004064</v>
+        <v>-11.42771038996593</v>
       </c>
       <c r="F73">
-        <v>-2.541336076785069</v>
+        <v>-1.124960356782362</v>
       </c>
       <c r="G73">
-        <v>-8.469780011374407</v>
+        <v>-4.701513610975074</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.0957952281808</v>
       </c>
       <c r="E74">
-        <v>-17.14435635082081</v>
+        <v>-11.49611751832579</v>
       </c>
       <c r="F74">
-        <v>-2.712712866913245</v>
+        <v>-1.279541997818778</v>
       </c>
       <c r="G74">
-        <v>-7.825348097099464</v>
+        <v>-5.133397836293866</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.006219360446807</v>
       </c>
       <c r="E75">
-        <v>-17.92035565677521</v>
+        <v>-10.72787548834654</v>
       </c>
       <c r="F75">
-        <v>-2.731628636556171</v>
+        <v>-1.312578946577228</v>
       </c>
       <c r="G75">
-        <v>-8.093702802338651</v>
+        <v>-4.531152587608704</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.924651052548868</v>
       </c>
       <c r="E76">
-        <v>-18.05209802260635</v>
+        <v>-12.20512710828472</v>
       </c>
       <c r="F76">
-        <v>-2.857547108720919</v>
+        <v>-1.680946475295543</v>
       </c>
       <c r="G76">
-        <v>-8.738905803680062</v>
+        <v>-4.99156047194375</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.853146119366897</v>
       </c>
       <c r="E77">
-        <v>-18.00390600221673</v>
+        <v>-12.21983559186163</v>
       </c>
       <c r="F77">
-        <v>-2.582095066472416</v>
+        <v>-1.656773886114451</v>
       </c>
       <c r="G77">
-        <v>-8.347433103087392</v>
+        <v>-4.293936674968649</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.795857162865775</v>
       </c>
       <c r="E78">
-        <v>-18.22506761580333</v>
+        <v>-12.62264788331792</v>
       </c>
       <c r="F78">
-        <v>-2.696375804995233</v>
+        <v>-1.383543525240256</v>
       </c>
       <c r="G78">
-        <v>-7.854879091134467</v>
+        <v>-4.227026004928452</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.750188431525106</v>
       </c>
       <c r="E79">
-        <v>-18.87540629651888</v>
+        <v>-13.53686527293443</v>
       </c>
       <c r="F79">
-        <v>-2.736194597680402</v>
+        <v>-1.634431160526142</v>
       </c>
       <c r="G79">
-        <v>-7.56620049955608</v>
+        <v>-4.072706873766208</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.714278676374597</v>
       </c>
       <c r="E80">
-        <v>-19.6560835161232</v>
+        <v>-14.15359814803905</v>
       </c>
       <c r="F80">
-        <v>-2.989690761917704</v>
+        <v>-1.997471458477054</v>
       </c>
       <c r="G80">
-        <v>-8.36457748573549</v>
+        <v>-3.494975631351658</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.68107947464162</v>
       </c>
       <c r="E81">
-        <v>-20.10918451143466</v>
+        <v>-13.06656513334183</v>
       </c>
       <c r="F81">
-        <v>-2.853954479294977</v>
+        <v>-1.574725751601965</v>
       </c>
       <c r="G81">
-        <v>-7.540682439488279</v>
+        <v>-3.28206044558085</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.642259369568793</v>
       </c>
       <c r="E82">
-        <v>-20.8748815390216</v>
+        <v>-14.18176525636676</v>
       </c>
       <c r="F82">
-        <v>-2.655341797330157</v>
+        <v>-1.764686964411948</v>
       </c>
       <c r="G82">
-        <v>-7.65129241825716</v>
+        <v>-3.07151758299752</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.588791611734234</v>
       </c>
       <c r="E83">
-        <v>-21.64998420712248</v>
+        <v>-15.83265215518104</v>
       </c>
       <c r="F83">
-        <v>-3.111141848679154</v>
+        <v>-1.806797849700663</v>
       </c>
       <c r="G83">
-        <v>-7.862422619499631</v>
+        <v>-3.378479141105132</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.509952004424234</v>
       </c>
       <c r="E84">
-        <v>-21.4858723090845</v>
+        <v>-15.04444861177598</v>
       </c>
       <c r="F84">
-        <v>-3.033633995901412</v>
+        <v>-1.309056728380525</v>
       </c>
       <c r="G84">
-        <v>-7.550450636070746</v>
+        <v>-2.913310204287333</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.401390763241256</v>
       </c>
       <c r="E85">
-        <v>-23.12641617326527</v>
+        <v>-18.21803036719541</v>
       </c>
       <c r="F85">
-        <v>-2.936690158751786</v>
+        <v>-1.736051960031974</v>
       </c>
       <c r="G85">
-        <v>-7.251823380724122</v>
+        <v>-2.959555740946147</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.259482775412502</v>
       </c>
       <c r="E86">
-        <v>-23.58610156978389</v>
+        <v>-17.7435866738858</v>
       </c>
       <c r="F86">
-        <v>-2.822472376151582</v>
+        <v>-1.814828871670805</v>
       </c>
       <c r="G86">
-        <v>-6.596458436213111</v>
+        <v>-2.743821985855776</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.088591743882147</v>
       </c>
       <c r="E87">
-        <v>-24.0026260805354</v>
+        <v>-20.27017629088135</v>
       </c>
       <c r="F87">
-        <v>-3.074685399281948</v>
+        <v>-1.665264651993146</v>
       </c>
       <c r="G87">
-        <v>-6.757353135380482</v>
+        <v>-3.179466491081691</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.897411707103023</v>
       </c>
       <c r="E88">
-        <v>-25.43119660489112</v>
+        <v>-20.80057380902974</v>
       </c>
       <c r="F88">
-        <v>-2.924258849137974</v>
+        <v>-2.039659381934229</v>
       </c>
       <c r="G88">
-        <v>-6.708840274624093</v>
+        <v>-1.856674831607149</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.698740271399875</v>
       </c>
       <c r="E89">
-        <v>-26.89493525839041</v>
+        <v>-21.70307150791439</v>
       </c>
       <c r="F89">
-        <v>-3.053446059074168</v>
+        <v>-1.950176649981619</v>
       </c>
       <c r="G89">
-        <v>-6.481198966494496</v>
+        <v>-2.003224030116628</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.511532475118808</v>
       </c>
       <c r="E90">
-        <v>-27.6501533971236</v>
+        <v>-23.29717134267249</v>
       </c>
       <c r="F90">
-        <v>-2.653442350875537</v>
+        <v>-2.161097214817234</v>
       </c>
       <c r="G90">
-        <v>-6.526437168134561</v>
+        <v>-2.628093301454161</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.353604497660335</v>
       </c>
       <c r="E91">
-        <v>-29.88640443159138</v>
+        <v>-24.68441048476021</v>
       </c>
       <c r="F91">
-        <v>-3.098055300449727</v>
+        <v>-2.328054664851475</v>
       </c>
       <c r="G91">
-        <v>-6.465248948494035</v>
+        <v>-2.114818375353343</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.247584674101426</v>
       </c>
       <c r="E92">
-        <v>-31.50032992555505</v>
+        <v>-26.32170743307747</v>
       </c>
       <c r="F92">
-        <v>-3.031508405145829</v>
+        <v>-2.071926777375479</v>
       </c>
       <c r="G92">
-        <v>-5.972589937451208</v>
+        <v>-2.25204562341244</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.214245791427344</v>
       </c>
       <c r="E93">
-        <v>-33.96326504766179</v>
+        <v>-29.64084340005144</v>
       </c>
       <c r="F93">
-        <v>-3.003851702668562</v>
+        <v>-1.620073068333418</v>
       </c>
       <c r="G93">
-        <v>-6.356932543595206</v>
+        <v>-3.079937197519055</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.271970076355028</v>
       </c>
       <c r="E94">
-        <v>-35.03784928731193</v>
+        <v>-30.11020614552445</v>
       </c>
       <c r="F94">
-        <v>-2.78847617794069</v>
+        <v>-1.781766243522868</v>
       </c>
       <c r="G94">
-        <v>-6.759049526926716</v>
+        <v>-2.019141235901495</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.437352307165158</v>
       </c>
       <c r="E95">
-        <v>-36.67439903741792</v>
+        <v>-34.15454099703477</v>
       </c>
       <c r="F95">
-        <v>-2.817986766665423</v>
+        <v>-1.808407367564303</v>
       </c>
       <c r="G95">
-        <v>-7.062076900384554</v>
+        <v>-1.924642054989487</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.721952861191373</v>
       </c>
       <c r="E96">
-        <v>-39.80574145153081</v>
+        <v>-34.38047109375145</v>
       </c>
       <c r="F96">
-        <v>-2.769392249714995</v>
+        <v>-2.244261988588693</v>
       </c>
       <c r="G96">
-        <v>-7.045477200515323</v>
+        <v>-2.777654661355211</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.119038995261414</v>
       </c>
       <c r="E97">
-        <v>-40.96288430081479</v>
+        <v>-37.53855414687963</v>
       </c>
       <c r="F97">
-        <v>-2.560268413776052</v>
+        <v>-1.616276660526388</v>
       </c>
       <c r="G97">
-        <v>-7.333132050967163</v>
+        <v>-3.194294331308822</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.635014341628705</v>
       </c>
       <c r="E98">
-        <v>-43.26448347945025</v>
+        <v>-40.55957614145466</v>
       </c>
       <c r="F98">
-        <v>-2.669784382997966</v>
+        <v>-1.565736308546785</v>
       </c>
       <c r="G98">
-        <v>-7.24137925250041</v>
+        <v>-2.662424722630631</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.226512188266683</v>
       </c>
       <c r="E99">
-        <v>-45.36066654862378</v>
+        <v>-42.86778236366732</v>
       </c>
       <c r="F99">
-        <v>-2.489090944690504</v>
+        <v>-1.811736576156154</v>
       </c>
       <c r="G99">
-        <v>-7.406434540605158</v>
+        <v>-2.808777047846544</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.914087777849086</v>
       </c>
       <c r="E100">
-        <v>-47.09424338281812</v>
+        <v>-45.45304288990624</v>
       </c>
       <c r="F100">
-        <v>-2.433532342984742</v>
+        <v>-1.837636311372083</v>
       </c>
       <c r="G100">
-        <v>-7.816902232805454</v>
+        <v>-2.593400945906152</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.60111547253105</v>
       </c>
       <c r="E101">
-        <v>-49.78677440135075</v>
+        <v>-47.22472456863813</v>
       </c>
       <c r="F101">
-        <v>-2.682069071581483</v>
+        <v>-1.735827472465816</v>
       </c>
       <c r="G101">
-        <v>-7.853602695947843</v>
+        <v>-3.63264256309972</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.382077501862717</v>
       </c>
       <c r="E102">
-        <v>-52.68606082553308</v>
+        <v>-49.73708119182758</v>
       </c>
       <c r="F102">
-        <v>-2.525377578770136</v>
+        <v>-1.293796544086152</v>
       </c>
       <c r="G102">
-        <v>-8.179841430717193</v>
+        <v>-3.29795140159324</v>
       </c>
     </row>
   </sheetData>
